--- a/liquidacion_final.xlsx
+++ b/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="953" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F652D429-1FF5-426B-9D4A-51187F991DBC}"/>
+  <xr:revisionPtr revIDLastSave="956" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556B65D6-D993-4231-BB15-97BEAB9AAD03}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -8206,7 +8206,7 @@
         <v>46085</v>
       </c>
       <c r="B289" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C289">
         <v>43262406</v>

--- a/liquidacion_final.xlsx
+++ b/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="956" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{556B65D6-D993-4231-BB15-97BEAB9AAD03}"/>
+  <xr:revisionPtr revIDLastSave="961" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1282943-7AE5-48E8-8691-97EF7BB24A37}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -17540,7 +17540,7 @@
         <v>46092</v>
       </c>
       <c r="B648" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C648">
         <v>1017250353</v>
@@ -20712,7 +20712,7 @@
         <v>46092</v>
       </c>
       <c r="B770" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C770">
         <v>1017250353</v>
@@ -28824,7 +28824,7 @@
         <v>46092</v>
       </c>
       <c r="B1082" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C1082">
         <v>1017250353</v>
@@ -51730,7 +51730,7 @@
         <v>46083</v>
       </c>
       <c r="B1963" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C1963">
         <v>1017250353</v>
@@ -60726,7 +60726,7 @@
         <v>46092</v>
       </c>
       <c r="B2309" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C2309">
         <v>1017250353</v>

--- a/liquidacion_final.xlsx
+++ b/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="961" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1282943-7AE5-48E8-8691-97EF7BB24A37}"/>
+  <xr:revisionPtr revIDLastSave="964" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD97A7CC-0BEB-40E0-A68C-5D95B91B84B9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10404" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10403" uniqueCount="95">
   <si>
     <t>Sucursal</t>
   </si>
@@ -6177,8 +6177,8 @@
       <c r="A211" s="2">
         <v>46088</v>
       </c>
-      <c r="B211" t="s">
-        <v>44</v>
+      <c r="B211" s="2">
+        <v>46088</v>
       </c>
       <c r="C211">
         <v>1017250353</v>

--- a/liquidacion_final.xlsx
+++ b/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="964" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD97A7CC-0BEB-40E0-A68C-5D95B91B84B9}"/>
+  <xr:revisionPtr revIDLastSave="967" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A52AFB1-AB74-412B-89E4-BF7477AD6338}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10403" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10404" uniqueCount="95">
   <si>
     <t>Sucursal</t>
   </si>
@@ -6177,8 +6177,8 @@
       <c r="A211" s="2">
         <v>46088</v>
       </c>
-      <c r="B211" s="2">
-        <v>46088</v>
+      <c r="B211" t="s">
+        <v>44</v>
       </c>
       <c r="C211">
         <v>1017250353</v>
